--- a/frontend/public/samples/sample-estimate.xlsx
+++ b/frontend/public/samples/sample-estimate.xlsx
@@ -1,37 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Div 03" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Exclusions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Div 03" sheetId="2" r:id="rId2"/>
+    <sheet name="Assumptions" sheetId="3" r:id="rId3"/>
+    <sheet name="Exclusions" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,374 +40,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -448,12 +79,15 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <f>'Div 03'!E8</f>
         <v>153140</v>
       </c>
       <c r="C2" t="n">
+        <f>'Div 03'!F8</f>
         <v>167005</v>
       </c>
       <c r="D2" t="n">
+        <f>B2+C2</f>
         <v>320145</v>
       </c>
     </row>
@@ -470,6 +104,7 @@
         <v>61200</v>
       </c>
       <c r="D3" t="n">
+        <f>B3+C3</f>
         <v>109800</v>
       </c>
     </row>
@@ -486,6 +121,7 @@
         <v>54900</v>
       </c>
       <c r="D4" t="n">
+        <f>B4+C4</f>
         <v>141300</v>
       </c>
     </row>
@@ -502,6 +138,7 @@
         <v>31500</v>
       </c>
       <c r="D5" t="n">
+        <f>B5+C5</f>
         <v>53600</v>
       </c>
     </row>
@@ -518,6 +155,7 @@
         <v>29400</v>
       </c>
       <c r="D6" t="n">
+        <f>B6+C6</f>
         <v>68150</v>
       </c>
     </row>
@@ -534,6 +172,7 @@
         <v>52800</v>
       </c>
       <c r="D7" t="n">
+        <f>B7+C7</f>
         <v>94000</v>
       </c>
     </row>
@@ -544,12 +183,15 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <f>SUM(B2:B7)</f>
         <v>390190</v>
       </c>
       <c r="C8" t="n">
+        <f>SUM(C2:C7)</f>
         <v>396805</v>
       </c>
       <c r="D8" t="n">
+        <f>SUM(D2:D7)</f>
         <v>786995</v>
       </c>
     </row>
@@ -573,23 +215,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Illustrative sample pricing. Figures match the on-site workbook samples.</t>
+          <t>Illustrative sample. Div 03 totals are live formulas from the Div 03 sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -654,6 +291,7 @@
         <v>14880</v>
       </c>
       <c r="G2" t="n">
+        <f>E2+F2</f>
         <v>33480</v>
       </c>
     </row>
@@ -683,6 +321,7 @@
         <v>30780</v>
       </c>
       <c r="G3" t="n">
+        <f>E3+F3</f>
         <v>58140</v>
       </c>
     </row>
@@ -712,6 +351,7 @@
         <v>27360</v>
       </c>
       <c r="G4" t="n">
+        <f>E4+F4</f>
         <v>37620</v>
       </c>
     </row>
@@ -741,6 +381,7 @@
         <v>46625</v>
       </c>
       <c r="G5" t="n">
+        <f>E5+F5</f>
         <v>121225</v>
       </c>
     </row>
@@ -770,6 +411,7 @@
         <v>14880</v>
       </c>
       <c r="G6" t="n">
+        <f>E6+F6</f>
         <v>37200</v>
       </c>
     </row>
@@ -792,10 +434,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
       <c r="F7" t="n">
         <v>32480</v>
       </c>
       <c r="G7" t="n">
+        <f>E7+F7</f>
         <v>32480</v>
       </c>
     </row>
@@ -806,12 +452,15 @@
         </is>
       </c>
       <c r="E8" t="n">
+        <f>SUM(E2:E7)</f>
         <v>153140</v>
       </c>
       <c r="F8" t="n">
+        <f>SUM(F2:F7)</f>
         <v>167005</v>
       </c>
       <c r="G8" t="n">
+        <f>SUM(G2:G7)</f>
         <v>320145</v>
       </c>
     </row>
@@ -823,95 +472,105 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Placement CY is the sum of footing, wall, and slab volumes (~92 + 84 + 288 CY). Illustrative pricing.</t>
+          <t>Placement CY is the sum of footing, wall, and slab volumes (~92 + 84 + 288 CY = 464 CY). Illustrative pricing.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Illustrative warehouse shell sample for QuantSult marketing site.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4,000 PSI mix per Spec 03 30 00</t>
+          <t>Div 03 quantities measured from S-101 through S-108.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quantities from sheets S-101 through S-108</t>
+          <t>Placement CY = footing + wall + slab volumes (~92 + 84 + 288).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pricing illustrative — align to project location</t>
+          <t>Other division totals are illustrative for the same warehouse shell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Pricing should be aligned to the project location before use in a live bid.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Testing and special inspection</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rock excavation</t>
+          <t>Dewatering, shoring and underpinning</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Winter protection / heated enclosure</t>
+          <t>Winter protection and heated enclosures</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Testing beyond owner allowance</t>
+          <t>Precast concrete (Division 03 40 00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sitework concrete beyond the building line (Division 32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Permit and impact fees</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/frontend/public/samples/sample-estimate.xlsx
+++ b/frontend/public/samples/sample-estimate.xlsx
@@ -128,7 +128,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06 Wood &amp; Plastics</t>
+          <t>06 Wood, Plastics, and Composites</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -145,7 +145,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07 Thermal &amp; Moisture</t>
+          <t>07 Thermal &amp; Moisture Protection</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -179,7 +179,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sample total</t>
+          <t>Subtotal, divisions shown</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -215,7 +215,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Illustrative sample. Div 03 totals are live formulas from the Div 03 sheet.</t>
+          <t>Illustrative sample — divisions shown only. Div 08 Openings omitted. Div 03 totals are live formulas from the Div 03 sheet.</t>
         </is>
       </c>
     </row>
